--- a/artfynd/A 36207-2023 artfynd.xlsx
+++ b/artfynd/A 36207-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36207-2023 artfynd.xlsx
+++ b/artfynd/A 36207-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91796630</v>
+        <v>91796641</v>
       </c>
       <c r="B2" t="n">
-        <v>85253</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1988</v>
+        <v>620</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,14 +710,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lorås, Jmt</t>
+          <t>Flakaflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514847.7312236757</v>
+        <v>514983</v>
       </c>
       <c r="R2" t="n">
-        <v>7041187.96978538</v>
+        <v>7041122</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-08-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-08-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,37 +788,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91796639</v>
+        <v>91796642</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>620</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -847,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514898.6452298125</v>
+        <v>514991</v>
       </c>
       <c r="R3" t="n">
-        <v>7041203.39332492</v>
+        <v>7041110</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,19 +860,9 @@
           <t>2017-08-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-08-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,37 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91796631</v>
+        <v>91796630</v>
       </c>
       <c r="B4" t="n">
-        <v>85254</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>249228</v>
+        <v>1988</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -975,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514897.8384371157</v>
+        <v>514848</v>
       </c>
       <c r="R4" t="n">
-        <v>7041184.630408837</v>
+        <v>7041188</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1008,19 +973,9 @@
           <t>2017-08-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-08-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1062,12 +1017,7 @@
         <v>91796640</v>
       </c>
       <c r="B5" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514954.3202416955</v>
+        <v>514954</v>
       </c>
       <c r="R5" t="n">
-        <v>7041157.202624013</v>
+        <v>7041157</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1136,19 +1086,9 @@
           <t>2017-08-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-08-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1187,37 +1127,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91796641</v>
+        <v>91796644</v>
       </c>
       <c r="B6" t="n">
-        <v>96332</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>620</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1231,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514982.6601824154</v>
+        <v>514954</v>
       </c>
       <c r="R6" t="n">
-        <v>7041122.496697041</v>
+        <v>7041066</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1264,19 +1199,9 @@
           <t>2017-08-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-08-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1315,37 +1240,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>91796642</v>
+        <v>91796639</v>
       </c>
       <c r="B7" t="n">
-        <v>96332</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>620</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1359,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514990.7715252303</v>
+        <v>514899</v>
       </c>
       <c r="R7" t="n">
-        <v>7041109.58177095</v>
+        <v>7041203</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1392,19 +1312,9 @@
           <t>2017-08-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2017-08-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1436,6 +1346,119 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>91796631</v>
+      </c>
+      <c r="B8" t="n">
+        <v>87323</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>249228</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Barrfagerspindling</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lorås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>514898</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7041185</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2017-08-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2017-08-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 36207-2023 artfynd.xlsx
+++ b/artfynd/A 36207-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91796641</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91796642</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91796630</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91796640</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91796644</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1350,6 +1380,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91796639</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1463,8 +1498,22 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91796631</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>